--- a/_ForDRA/BVSimulationFiles/76.xlsx
+++ b/_ForDRA/BVSimulationFiles/76.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0004137931034482759</v>
+        <v>0.008275862068965517</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0004163965879180762</v>
+        <v>0.008327931758361523</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0004189961046122556</v>
+        <v>0.008379922092245112</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0004215916578978272</v>
+        <v>0.008431833157956545</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000424183252137571</v>
+        <v>0.00848366504275142</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0004267708916900369</v>
+        <v>0.008535417833800739</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000429354580909548</v>
+        <v>0.00858709161819096</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0004319343241462057</v>
+        <v>0.008638686482924113</v>
       </c>
       <c r="J2" t="n">
-        <v>0.000434510125745893</v>
+        <v>0.008690202514917859</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0004370819900502775</v>
+        <v>0.008741639801005551</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000439649921396817</v>
+        <v>0.008792998427936339</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0004422139241187613</v>
+        <v>0.008844278482375225</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0004447740025451575</v>
+        <v>0.00889548005090315</v>
       </c>
       <c r="O2" t="n">
-        <v>0.000447330161000853</v>
+        <v>0.008946603220017061</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0004498824038064998</v>
+        <v>0.008997648076129997</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.000452430735278558</v>
+        <v>0.00904861470557116</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0004549751597292996</v>
+        <v>0.009099503194585992</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0004575156814668126</v>
+        <v>0.009150313629336252</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0004600523047950044</v>
+        <v>0.009201046095900087</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0004625850340136055</v>
+        <v>0.009251700680272111</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0004137931034482759</v>
+        <v>0.008275862068965517</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004163965879180762</v>
+        <v>0.008327931758361523</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0004189961046122556</v>
+        <v>0.008379922092245112</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0004215916578978272</v>
+        <v>0.008431833157956545</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000424183252137571</v>
+        <v>0.00848366504275142</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0004267708916900369</v>
+        <v>0.008535417833800739</v>
       </c>
       <c r="H3" t="n">
-        <v>0.000429354580909548</v>
+        <v>0.00858709161819096</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0004319343241462057</v>
+        <v>0.008638686482924113</v>
       </c>
       <c r="J3" t="n">
-        <v>0.000434510125745893</v>
+        <v>0.008690202514917859</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0004370819900502775</v>
+        <v>0.008741639801005551</v>
       </c>
       <c r="L3" t="n">
-        <v>0.000439649921396817</v>
+        <v>0.008792998427936339</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0004422139241187613</v>
+        <v>0.008844278482375225</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0004447740025451575</v>
+        <v>0.00889548005090315</v>
       </c>
       <c r="O3" t="n">
-        <v>0.000447330161000853</v>
+        <v>0.008946603220017061</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0004498824038064998</v>
+        <v>0.008997648076129997</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.000452430735278558</v>
+        <v>0.00904861470557116</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0004549751597292996</v>
+        <v>0.009099503194585992</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0004575156814668126</v>
+        <v>0.009150313629336252</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0004600523047950044</v>
+        <v>0.009201046095900087</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0004625850340136055</v>
+        <v>0.009251700680272111</v>
       </c>
     </row>
   </sheetData>
